--- a/public/assets/documents/excel/sample_upload/NominationProcess.xlsx
+++ b/public/assets/documents/excel/sample_upload/NominationProcess.xlsx
@@ -36,12 +36,6 @@
   </si>
   <si>
     <t>Employee Type</t>
-  </si>
-  <si>
-    <t>Last Taining Attended on (Date)</t>
-  </si>
-  <si>
-    <t>Last Training Attended on (Topic)</t>
   </si>
 </sst>
 </file>
@@ -376,12 +370,6 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/assets/documents/excel/sample_upload/NominationProcess.xlsx
+++ b/public/assets/documents/excel/sample_upload/NominationProcess.xlsx
@@ -23,19 +23,13 @@
     <t>SNo</t>
   </si>
   <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>Email ID</t>
-  </si>
-  <si>
     <t>Department</t>
   </si>
   <si>
-    <t>Employee Type</t>
+    <t>Employee/Worker</t>
+  </si>
+  <si>
+    <t>Employee/Worker ID</t>
   </si>
 </sst>
 </file>
@@ -343,7 +337,7 @@
   <sheetFormatPr defaultColWidth="8.886719" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="17.10938" customWidth="1"/>
+    <col min="3" max="3" width="21.85547" customWidth="1"/>
     <col min="4" max="4" width="34.71094" customWidth="1"/>
     <col min="5" max="5" width="27.28516" customWidth="1"/>
     <col min="6" max="6" width="21.14063" customWidth="1"/>
@@ -364,12 +358,6 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
